--- a/All_Code/Q2/Results/Tables/monthly_metrics.xlsx
+++ b/All_Code/Q2/Results/Tables/monthly_metrics.xlsx
@@ -505,25 +505,25 @@
         <v>0.0595081329835421</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006341425555716813</v>
+        <v>0.004109099232228196</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06368504142636573</v>
+        <v>0.1068658741134411</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06557089745573737</v>
+        <v>0.09564116191249201</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1285404.641787025</v>
+        <v>1395783.447733032</v>
       </c>
       <c r="K2" t="n">
-        <v>74472.59021036024</v>
+        <v>48074.30227852617</v>
       </c>
       <c r="L2" t="n">
-        <v>1359877.231997386</v>
+        <v>1443857.750011558</v>
       </c>
       <c r="M2" t="n">
         <v>28</v>
@@ -549,25 +549,25 @@
         <v>0.0737711679118562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008907581464482912</v>
+        <v>0.006607294747760313</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05342856493499454</v>
+        <v>0.08354826092805237</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0931365726274845</v>
+        <v>0.1139810457343821</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1173149.56394357</v>
+        <v>1242251.330486828</v>
       </c>
       <c r="K3" t="n">
-        <v>109934.4517074384</v>
+        <v>79463.82199848469</v>
       </c>
       <c r="L3" t="n">
-        <v>1283084.015651009</v>
+        <v>1321715.152485312</v>
       </c>
       <c r="M3" t="n">
         <v>31</v>
@@ -593,25 +593,25 @@
         <v>0.06984629379633291</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008281860457949722</v>
+        <v>0.005664696962732892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06586053066994671</v>
+        <v>0.1088713674040239</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1249210896741351</v>
+        <v>0.1486609567659939</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1008225.465215799</v>
+        <v>1107677.284457787</v>
       </c>
       <c r="K4" t="n">
-        <v>97555.09067541265</v>
+        <v>68023.78034140145</v>
       </c>
       <c r="L4" t="n">
-        <v>1105780.555891211</v>
+        <v>1175701.064799189</v>
       </c>
       <c r="M4" t="n">
         <v>30</v>
@@ -637,25 +637,25 @@
         <v>0.0679221147459156</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01011201543539906</v>
+        <v>0.007649498474568341</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05605976302849745</v>
+        <v>0.07401191927404317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1218603019967869</v>
+        <v>0.1375221125275634</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>981682.4240835753</v>
+        <v>1021935.413576234</v>
       </c>
       <c r="K5" t="n">
-        <v>134969.8814369425</v>
+        <v>104430.7161926771</v>
       </c>
       <c r="L5" t="n">
-        <v>1116652.305520518</v>
+        <v>1126366.129768912</v>
       </c>
       <c r="M5" t="n">
         <v>31</v>
@@ -681,25 +681,25 @@
         <v>0.0898498308800704</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01266559290654156</v>
+        <v>0.007819039669348916</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06305307666943608</v>
+        <v>0.08308570534300734</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07136571750153671</v>
+        <v>0.09414756200469787</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1290640.32363503</v>
+        <v>1363321.560510243</v>
       </c>
       <c r="K6" t="n">
-        <v>167922.5949419815</v>
+        <v>101758.7325537183</v>
       </c>
       <c r="L6" t="n">
-        <v>1458562.918577011</v>
+        <v>1465080.293063961</v>
       </c>
       <c r="M6" t="n">
         <v>30</v>
@@ -725,25 +725,25 @@
         <v>0.0722704305394401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01222737184953064</v>
+        <v>0.009463189879717003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05651749389009533</v>
+        <v>0.07413032112439161</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07328163993651264</v>
+        <v>0.08300307428836298</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1436881.850835775</v>
+        <v>1493520.831973986</v>
       </c>
       <c r="K7" t="n">
-        <v>180672.4184597885</v>
+        <v>136112.1653732629</v>
       </c>
       <c r="L7" t="n">
-        <v>1617554.269295564</v>
+        <v>1629632.997347249</v>
       </c>
       <c r="M7" t="n">
         <v>31</v>
@@ -769,25 +769,25 @@
         <v>0.0683657233502849</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008927071843149828</v>
+        <v>0.006768663780533081</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05448901023213393</v>
+        <v>0.08055557794156759</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1168564212652276</v>
+        <v>0.1355582738498574</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1274810.30792931</v>
+        <v>1347866.214444197</v>
       </c>
       <c r="K8" t="n">
-        <v>125253.7833630091</v>
+        <v>95635.87920003245</v>
       </c>
       <c r="L8" t="n">
-        <v>1400064.091292319</v>
+        <v>1443502.09364423</v>
       </c>
       <c r="M8" t="n">
         <v>31</v>
@@ -813,25 +813,25 @@
         <v>0.0692234685223922</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009398857272936566</v>
+        <v>0.006718794338162267</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07239078032809959</v>
+        <v>0.09781630053717713</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1181120559569453</v>
+        <v>0.1337842451454954</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1137407.905131412</v>
+        <v>1197407.763015437</v>
       </c>
       <c r="K9" t="n">
-        <v>126820.2670064084</v>
+        <v>89130.85452476458</v>
       </c>
       <c r="L9" t="n">
-        <v>1264228.172137821</v>
+        <v>1286538.617540201</v>
       </c>
       <c r="M9" t="n">
         <v>30</v>
@@ -857,25 +857,25 @@
         <v>0.0612482074336168</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003259000951322897</v>
+        <v>0.002186928704382982</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1245124480525588</v>
+        <v>0.1434509134581231</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1306498860910303</v>
+        <v>0.1432409536454206</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1301544.191165422</v>
+        <v>1355785.891179741</v>
       </c>
       <c r="K10" t="n">
-        <v>40636.93485929138</v>
+        <v>26851.20770262993</v>
       </c>
       <c r="L10" t="n">
-        <v>1342181.126024714</v>
+        <v>1382637.098882371</v>
       </c>
       <c r="M10" t="n">
         <v>31</v>
@@ -901,25 +901,25 @@
         <v>0.050998187756857</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003615175074999621</v>
+        <v>0.002416320192136663</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1017408953391965</v>
+        <v>0.1179188756381131</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1009071720156001</v>
+        <v>0.1142525394779924</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1451090.806046234</v>
+        <v>1495716.414141194</v>
       </c>
       <c r="K11" t="n">
-        <v>40502.24845430129</v>
+        <v>26607.64512403293</v>
       </c>
       <c r="L11" t="n">
-        <v>1491593.054500536</v>
+        <v>1522324.059265228</v>
       </c>
       <c r="M11" t="n">
         <v>30</v>
@@ -945,25 +945,25 @@
         <v>0.0530561177235946</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006244733892304897</v>
+        <v>0.005277443520090788</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05249477717359249</v>
+        <v>0.0735509003768498</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04963308901828073</v>
+        <v>0.06316362092309788</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1724990.424171994</v>
+        <v>1776477.21417709</v>
       </c>
       <c r="K12" t="n">
-        <v>76626.73644639294</v>
+        <v>63697.35239652172</v>
       </c>
       <c r="L12" t="n">
-        <v>1801617.160618387</v>
+        <v>1840174.566573611</v>
       </c>
       <c r="M12" t="n">
         <v>31</v>
